--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.1389,0.8300,0.0612,0.0020</t>
-  </si>
-  <si>
-    <t>0.1230,0.0076,0.0752,0.8493</t>
-  </si>
-  <si>
-    <t>0.6034,0.2632,0.1072,0.0088</t>
-  </si>
-  <si>
-    <t>0.3625,0.0157,0.1576,0.4620</t>
-  </si>
-  <si>
-    <t>0.9022,0.1122,0.0047,0.0011</t>
-  </si>
-  <si>
-    <t>0.7998,0.1981,0.0136,0.0019</t>
-  </si>
-  <si>
-    <t>0.7498,0.2583,0.0154,0.0017</t>
-  </si>
-  <si>
-    <t>0.8011,0.2263,0.0094,0.0015</t>
-  </si>
-  <si>
-    <t>0.7570,0.2510,0.0141,0.0020</t>
-  </si>
-  <si>
-    <t>0.6130,0.4045,0.0195,0.0017</t>
-  </si>
-  <si>
-    <t>0.9087,0.0966,0.0054,0.0016</t>
-  </si>
-  <si>
-    <t>0.8508,0.1411,0.0117,0.0019</t>
-  </si>
-  <si>
-    <t>0.0499,0.8871,0.1611,0.0010</t>
-  </si>
-  <si>
-    <t>0.0060,0.1543,0.9560,0.0001</t>
-  </si>
-  <si>
-    <t>0.0109,0.6838,0.7110,0.0002</t>
-  </si>
-  <si>
-    <t>0.0482,0.3836,0.6531,0.0007</t>
-  </si>
-  <si>
-    <t>0.0332,0.8017,0.3853,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0159,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9987,0.0372,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.9911,0.0469,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0165,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0154,0.0000</t>
-  </si>
-  <si>
-    <t>0.1735,0.1839,0.5510,0.0019</t>
-  </si>
-  <si>
-    <t>0.1891,0.0599,0.6790,0.0017</t>
-  </si>
-  <si>
-    <t>0.0011,0.0153,0.9953,0.0001</t>
-  </si>
-  <si>
-    <t>0.2416,0.1261,0.5139,0.0033</t>
-  </si>
-  <si>
-    <t>0.0151,0.5396,0.7634,0.0004</t>
-  </si>
-  <si>
-    <t>0.0324,0.0210,0.9469,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.0072,0.9963,0.0002</t>
-  </si>
-  <si>
-    <t>0.0023,0.9932,0.0501,0.0000</t>
-  </si>
-  <si>
-    <t>0.1022,0.5392,0.4065,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.0986,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.9586,0.4661,0.0001</t>
-  </si>
-  <si>
-    <t>0.1484,0.7916,0.0753,0.0014</t>
-  </si>
-  <si>
-    <t>0.0169,0.9283,0.2205,0.0004</t>
-  </si>
-  <si>
-    <t>0.0223,0.9388,0.1300,0.0004</t>
-  </si>
-  <si>
-    <t>0.0034,0.9864,0.1062,0.0001</t>
-  </si>
-  <si>
-    <t>0.0178,0.9405,0.2324,0.0010</t>
-  </si>
-  <si>
-    <t>0.1835,0.3617,0.4054,0.0037</t>
-  </si>
-  <si>
-    <t>0.0089,0.9018,0.5656,0.0004</t>
-  </si>
-  <si>
-    <t>0.0113,0.0294,0.9733,0.0003</t>
-  </si>
-  <si>
-    <t>0.0191,0.6990,0.6381,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.9972,0.0233,0.0001</t>
-  </si>
-  <si>
-    <t>0.0156,0.3762,0.8441,0.0004</t>
-  </si>
-  <si>
-    <t>0.3209,0.5099,0.1890,0.0130</t>
-  </si>
-  <si>
-    <t>0.0010,0.9984,0.0111,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9985,0.0231,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0169,0.0000</t>
-  </si>
-  <si>
-    <t>0.0095,0.8475,0.6404,0.0008</t>
-  </si>
-  <si>
-    <t>0.0081,0.6377,0.8493,0.0004</t>
-  </si>
-  <si>
-    <t>0.0631,0.0126,0.9213,0.0006</t>
-  </si>
-  <si>
-    <t>0.0070,0.0236,0.9809,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.2375,0.9863,0.0001</t>
-  </si>
-  <si>
-    <t>0.0321,0.0693,0.9132,0.0008</t>
-  </si>
-  <si>
-    <t>0.1746,0.7478,0.0766,0.0014</t>
-  </si>
-  <si>
-    <t>0.3904,0.5268,0.0607,0.0019</t>
-  </si>
-  <si>
-    <t>0.2693,0.7016,0.0382,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.1199,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.6634,0.3310,0.0248,0.0024</t>
-  </si>
-  <si>
-    <t>0.3799,0.5977,0.0334,0.0015</t>
-  </si>
-  <si>
-    <t>0.1029,0.8619,0.0445,0.0009</t>
-  </si>
-  <si>
-    <t>0.0073,0.9701,0.2109,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.8527,0.9235,0.0001</t>
-  </si>
-  <si>
-    <t>0.0070,0.8375,0.6770,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.9796,0.5657,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0594,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9988,0.0234,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0697,0.5313,0.4917,0.0009</t>
-  </si>
-  <si>
-    <t>0.0126,0.8964,0.3747,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.9376,0.7669,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.9796,0.3039,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.9837,0.2733,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.9896,0.0582,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.9872,0.2571,0.0001</t>
-  </si>
-  <si>
-    <t>0.3243,0.0049,0.5008,0.1769</t>
-  </si>
-  <si>
-    <t>0.0048,0.0016,0.0058,0.9964</t>
-  </si>
-  <si>
-    <t>0.0112,0.0017,0.0055,0.9929</t>
-  </si>
-  <si>
-    <t>0.2005,0.0032,0.1593,0.6816</t>
-  </si>
-  <si>
-    <t>0.2926,0.0184,0.1511,0.5395</t>
-  </si>
-  <si>
-    <t>0.0249,0.0097,0.0138,0.9796</t>
-  </si>
-  <si>
-    <t>0.0039,0.9831,0.2124,0.0002</t>
-  </si>
-  <si>
-    <t>0.0062,0.9736,0.2650,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.9552,0.6157,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.9648,0.3346,0.0004</t>
-  </si>
-  <si>
-    <t>0.0048,0.9756,0.2583,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.9850,0.2981,0.0001</t>
-  </si>
-  <si>
-    <t>0.3324,0.6165,0.0465,0.0017</t>
-  </si>
-  <si>
-    <t>0.1856,0.7616,0.0508,0.0012</t>
-  </si>
-  <si>
-    <t>0.1126,0.8193,0.0717,0.0009</t>
-  </si>
-  <si>
-    <t>0.6904,0.3151,0.0188,0.0023</t>
-  </si>
-  <si>
-    <t>0.6831,0.3373,0.0161,0.0020</t>
-  </si>
-  <si>
-    <t>0.9399,0.0589,0.0040,0.0015</t>
-  </si>
-  <si>
-    <t>0.5038,0.4748,0.0330,0.0023</t>
-  </si>
-  <si>
-    <t>0.2144,0.7138,0.0607,0.0013</t>
-  </si>
-  <si>
-    <t>0.8641,0.1605,0.0061,0.0012</t>
-  </si>
-  <si>
-    <t>0.7624,0.2530,0.0131,0.0015</t>
-  </si>
-  <si>
-    <t>0.8570,0.1581,0.0074,0.0017</t>
-  </si>
-  <si>
-    <t>0.5286,0.4845,0.0239,0.0019</t>
-  </si>
-  <si>
-    <t>0.6611,0.3552,0.0196,0.0021</t>
-  </si>
-  <si>
-    <t>0.7295,0.2665,0.0206,0.0021</t>
-  </si>
-  <si>
-    <t>0.4077,0.6006,0.0259,0.0018</t>
-  </si>
-  <si>
-    <t>0.9231,0.0673,0.0072,0.0024</t>
-  </si>
-  <si>
-    <t>0.0001,0.0121,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0060,0.0897,0.9689,0.0002</t>
-  </si>
-  <si>
-    <t>0.3407,0.0989,0.4605,0.0043</t>
-  </si>
-  <si>
-    <t>0.0003,0.0447,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9987,0.0157,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9982,0.0266,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9963,0.0429,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.9893,0.0712,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0274,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0066,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.9921,0.0324,0.0001</t>
-  </si>
-  <si>
-    <t>0.0834,0.7494,0.2628,0.0015</t>
-  </si>
-  <si>
-    <t>0.2099,0.1097,0.5698,0.0019</t>
-  </si>
-  <si>
-    <t>0.0474,0.7624,0.3795,0.0013</t>
-  </si>
-  <si>
-    <t>0.1165,0.6784,0.2608,0.0022</t>
-  </si>
-  <si>
-    <t>0.0938,0.6089,0.4245,0.0030</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0073,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9989,0.0102,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9984,0.0161,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0195,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9976,0.0315,0.0000</t>
-  </si>
-  <si>
-    <t>0.0508,0.8909,0.1138,0.0006</t>
-  </si>
-  <si>
-    <t>0.0173,0.9440,0.1523,0.0003</t>
-  </si>
-  <si>
-    <t>0.2935,0.7025,0.0274,0.0012</t>
-  </si>
-  <si>
-    <t>0.5992,0.4278,0.0198,0.0021</t>
-  </si>
-  <si>
-    <t>0.4067,0.5941,0.0301,0.0019</t>
-  </si>
-  <si>
-    <t>0.5289,0.4336,0.0421,0.0026</t>
-  </si>
-  <si>
-    <t>0.6594,0.3845,0.0127,0.0014</t>
-  </si>
-  <si>
-    <t>0.2699,0.7164,0.0312,0.0012</t>
-  </si>
-  <si>
-    <t>0.6318,0.3270,0.0385,0.0029</t>
-  </si>
-  <si>
-    <t>0.4624,0.5252,0.0348,0.0022</t>
-  </si>
-  <si>
-    <t>0.0016,0.9608,0.6039,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9549,0.7868,0.0000</t>
-  </si>
-  <si>
-    <t>0.0054,0.8508,0.7347,0.0003</t>
-  </si>
-  <si>
-    <t>0.0205,0.4908,0.7699,0.0006</t>
-  </si>
-  <si>
-    <t>0.2878,0.4084,0.2627,0.0053</t>
-  </si>
-  <si>
-    <t>0.0706,0.6476,0.3859,0.0013</t>
-  </si>
-  <si>
-    <t>0.0900,0.0210,0.8815,0.0006</t>
-  </si>
-  <si>
-    <t>0.0867,0.8376,0.1307,0.0013</t>
-  </si>
-  <si>
-    <t>0.6560,0.0138,0.2571,0.0550</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.0012,0.9997</t>
-  </si>
-  <si>
-    <t>0.0056,0.0070,0.0068,0.9954</t>
-  </si>
-  <si>
-    <t>0.1899,0.0024,0.2531,0.6259</t>
-  </si>
-  <si>
-    <t>0.0008,0.9950,0.1560,0.0000</t>
-  </si>
-  <si>
-    <t>0.7478,0.2782,0.0137,0.0018</t>
-  </si>
-  <si>
-    <t>0.0220,0.9749,0.0142,0.0002</t>
-  </si>
-  <si>
-    <t>0.7085,0.2705,0.0290,0.0030</t>
-  </si>
-  <si>
-    <t>0.0172,0.9646,0.0528,0.0002</t>
-  </si>
-  <si>
-    <t>0.5031,0.4847,0.0376,0.0035</t>
-  </si>
-  <si>
-    <t>0.6723,0.1369,0.1471,0.0094</t>
-  </si>
-  <si>
-    <t>0.8144,0.1789,0.0158,0.0021</t>
-  </si>
-  <si>
-    <t>0.0010,0.7215,0.9234,0.0001</t>
-  </si>
-  <si>
-    <t>0.9559,0.0174,0.0093,0.0041</t>
-  </si>
-  <si>
-    <t>0.5626,0.4311,0.0293,0.0023</t>
-  </si>
-  <si>
-    <t>0.0094,0.9822,0.0366,0.0001</t>
-  </si>
-  <si>
-    <t>0.1724,0.7376,0.1077,0.0019</t>
-  </si>
-  <si>
-    <t>0.0314,0.9041,0.1825,0.0005</t>
-  </si>
-  <si>
-    <t>0.0086,0.9822,0.0602,0.0002</t>
-  </si>
-  <si>
-    <t>0.0247,0.8370,0.3621,0.0004</t>
-  </si>
-  <si>
-    <t>0.0444,0.9055,0.1219,0.0008</t>
-  </si>
-  <si>
-    <t>0.8465,0.1622,0.0096,0.0018</t>
-  </si>
-  <si>
-    <t>0.8928,0.0970,0.0096,0.0024</t>
-  </si>
-  <si>
-    <t>0.6788,0.3388,0.0196,0.0021</t>
-  </si>
-  <si>
-    <t>0.9320,0.0582,0.0074,0.0019</t>
-  </si>
-  <si>
-    <t>0.8898,0.1067,0.0081,0.0018</t>
-  </si>
-  <si>
-    <t>0.8702,0.1404,0.0078,0.0016</t>
-  </si>
-  <si>
-    <t>0.8533,0.1487,0.0103,0.0022</t>
-  </si>
-  <si>
-    <t>0.8109,0.2025,0.0118,0.0020</t>
-  </si>
-  <si>
-    <t>0.0032,0.9909,0.0590,0.0001</t>
-  </si>
-  <si>
-    <t>0.0303,0.9473,0.0473,0.0003</t>
-  </si>
-  <si>
-    <t>0.0065,0.9869,0.0293,0.0001</t>
-  </si>
-  <si>
-    <t>0.0566,0.8891,0.1151,0.0009</t>
-  </si>
-  <si>
-    <t>0.0455,0.9252,0.0575,0.0005</t>
-  </si>
-  <si>
-    <t>0.0893,0.8784,0.0496,0.0010</t>
-  </si>
-  <si>
-    <t>0.0268,0.9471,0.0650,0.0004</t>
-  </si>
-  <si>
-    <t>0.0678,0.8953,0.0630,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0689,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0590,0.8651,0.1511,0.0011</t>
-  </si>
-  <si>
-    <t>0.0001,0.0229,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0093,0.7917,0.7157,0.0004</t>
-  </si>
-  <si>
-    <t>0.0996,0.0231,0.8689,0.0008</t>
-  </si>
-  <si>
-    <t>0.0011,0.9233,0.7923,0.0001</t>
-  </si>
-  <si>
-    <t>0.0667,0.0735,0.8403,0.0006</t>
-  </si>
-  <si>
-    <t>0.0120,0.0086,0.9807,0.0002</t>
-  </si>
-  <si>
-    <t>0.0096,0.0974,0.9572,0.0002</t>
-  </si>
-  <si>
-    <t>0.0194,0.8562,0.4076,0.0005</t>
-  </si>
-  <si>
-    <t>0.0193,0.6885,0.6223,0.0004</t>
-  </si>
-  <si>
-    <t>0.0262,0.6487,0.6144,0.0005</t>
-  </si>
-  <si>
-    <t>0.0243,0.6852,0.5712,0.0005</t>
-  </si>
-  <si>
-    <t>0.0303,0.9339,0.1246,0.0006</t>
-  </si>
-  <si>
-    <t>0.0319,0.7679,0.4033,0.0005</t>
-  </si>
-  <si>
-    <t>0.0819,0.8062,0.1921,0.0017</t>
-  </si>
-  <si>
-    <t>0.0584,0.6514,0.4154,0.0010</t>
-  </si>
-  <si>
-    <t>0.0039,0.9882,0.0718,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9951,0.0550,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.9899,0.0610,0.0001</t>
-  </si>
-  <si>
-    <t>0.0740,0.8912,0.0512,0.0007</t>
-  </si>
-  <si>
-    <t>0.0111,0.9787,0.0315,0.0001</t>
-  </si>
-  <si>
-    <t>0.0348,0.9298,0.1093,0.0006</t>
-  </si>
-  <si>
-    <t>0.2245,0.3983,0.3057,0.0022</t>
-  </si>
-  <si>
-    <t>0.0662,0.7710,0.3008,0.0018</t>
-  </si>
-  <si>
-    <t>0.0510,0.5311,0.5371,0.0007</t>
-  </si>
-  <si>
-    <t>0.1795,0.1851,0.5628,0.0023</t>
-  </si>
-  <si>
-    <t>0.0352,0.2247,0.8132,0.0007</t>
-  </si>
-  <si>
-    <t>0.0721,0.3602,0.6275,0.0015</t>
-  </si>
-  <si>
-    <t>0.0197,0.5934,0.7237,0.0007</t>
-  </si>
-  <si>
-    <t>0.0341,0.6980,0.5781,0.0010</t>
-  </si>
-  <si>
-    <t>0.0042,0.5498,0.9063,0.0003</t>
-  </si>
-  <si>
-    <t>0.7996,0.2215,0.0100,0.0019</t>
-  </si>
-  <si>
-    <t>0.5543,0.4447,0.0258,0.0018</t>
-  </si>
-  <si>
-    <t>0.6480,0.3753,0.0178,0.0019</t>
-  </si>
-  <si>
-    <t>0.3790,0.5612,0.0508,0.0019</t>
-  </si>
-  <si>
-    <t>0.5000,0.4689,0.0333,0.0016</t>
-  </si>
-  <si>
-    <t>0.5188,0.4628,0.0292,0.0017</t>
-  </si>
-  <si>
-    <t>0.5529,0.4820,0.0180,0.0018</t>
-  </si>
-  <si>
-    <t>0.8164,0.1919,0.0111,0.0020</t>
-  </si>
-  <si>
-    <t>0.0051,0.0422,0.9823,0.0002</t>
-  </si>
-  <si>
-    <t>0.0372,0.9160,0.1331,0.0008</t>
-  </si>
-  <si>
-    <t>0.2576,0.4535,0.2490,0.0029</t>
-  </si>
-  <si>
-    <t>0.0005,0.0520,0.9953,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.6742,0.9094,0.0002</t>
-  </si>
-  <si>
-    <t>0.0103,0.8450,0.6027,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.1348,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.6820,0.8222,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0356,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0055,0.6685,0.8478,0.0004</t>
-  </si>
-  <si>
-    <t>0.0036,0.9002,0.6652,0.0002</t>
-  </si>
-  <si>
-    <t>0.0431,0.8317,0.2948,0.0012</t>
-  </si>
-  <si>
-    <t>0.3000,0.0848,0.4931,0.0019</t>
-  </si>
-  <si>
-    <t>0.1897,0.3913,0.3454,0.0016</t>
-  </si>
-  <si>
-    <t>0.5146,0.4844,0.0260,0.0019</t>
-  </si>
-  <si>
-    <t>0.1906,0.7437,0.0616,0.0015</t>
-  </si>
-  <si>
-    <t>0.8086,0.1829,0.0146,0.0019</t>
-  </si>
-  <si>
-    <t>0.2689,0.6659,0.0569,0.0017</t>
-  </si>
-  <si>
-    <t>0.8253,0.2012,0.0076,0.0018</t>
-  </si>
-  <si>
-    <t>0.2343,0.7030,0.0552,0.0014</t>
-  </si>
-  <si>
-    <t>0.3749,0.6022,0.0349,0.0018</t>
-  </si>
-  <si>
-    <t>0.7272,0.2956,0.0143,0.0018</t>
-  </si>
-  <si>
-    <t>0.0129,0.9402,0.2565,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.1166,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.8599,0.8601,0.0001</t>
-  </si>
-  <si>
-    <t>0.0157,0.6578,0.6860,0.0005</t>
-  </si>
-  <si>
-    <t>0.0107,0.1036,0.9513,0.0006</t>
-  </si>
-  <si>
-    <t>0.2354,0.0779,0.5840,0.0019</t>
-  </si>
-  <si>
-    <t>0.0423,0.1276,0.8505,0.0006</t>
-  </si>
-  <si>
-    <t>0.1340,0.4626,0.4254,0.0028</t>
-  </si>
-  <si>
-    <t>0.7042,0.0822,0.1754,0.0358</t>
-  </si>
-  <si>
-    <t>0.1209,0.1937,0.0615,0.8029</t>
-  </si>
-  <si>
-    <t>0.7397,0.0148,0.0191,0.1222</t>
-  </si>
-  <si>
-    <t>0.0325,0.0017,0.0593,0.9584</t>
-  </si>
-  <si>
-    <t>0.0147,0.0024,0.0241,0.9854</t>
-  </si>
-  <si>
-    <t>0.5868,0.1322,0.2488,0.0133</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.1107,0.8154,0.1216,0.0021</t>
+  </si>
+  <si>
+    <t>0.0514,0.0032,0.0635,0.9383</t>
+  </si>
+  <si>
+    <t>0.7158,0.2169,0.0540,0.0075</t>
+  </si>
+  <si>
+    <t>0.5612,0.0213,0.2498,0.1528</t>
+  </si>
+  <si>
+    <t>0.8162,0.2113,0.0086,0.0013</t>
+  </si>
+  <si>
+    <t>0.8466,0.1606,0.0090,0.0019</t>
+  </si>
+  <si>
+    <t>0.3073,0.6388,0.0515,0.0019</t>
+  </si>
+  <si>
+    <t>0.8308,0.1820,0.0093,0.0016</t>
+  </si>
+  <si>
+    <t>0.4685,0.5072,0.0322,0.0020</t>
+  </si>
+  <si>
+    <t>0.6035,0.4076,0.0211,0.0018</t>
+  </si>
+  <si>
+    <t>0.8153,0.2116,0.0082,0.0013</t>
+  </si>
+  <si>
+    <t>0.8858,0.1215,0.0066,0.0015</t>
+  </si>
+  <si>
+    <t>0.0428,0.8140,0.3002,0.0008</t>
+  </si>
+  <si>
+    <t>0.0066,0.0675,0.9710,0.0002</t>
+  </si>
+  <si>
+    <t>0.0267,0.4290,0.7295,0.0004</t>
+  </si>
+  <si>
+    <t>0.0404,0.2550,0.7692,0.0006</t>
+  </si>
+  <si>
+    <t>0.0151,0.7066,0.6708,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0264,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0374,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9947,0.0349,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0174,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0155,0.0000</t>
+  </si>
+  <si>
+    <t>0.2276,0.0296,0.6920,0.0013</t>
+  </si>
+  <si>
+    <t>0.1308,0.1736,0.6473,0.0018</t>
+  </si>
+  <si>
+    <t>0.0025,0.0277,0.9900,0.0001</t>
+  </si>
+  <si>
+    <t>0.0634,0.0297,0.8946,0.0011</t>
+  </si>
+  <si>
+    <t>0.0507,0.0782,0.8644,0.0007</t>
+  </si>
+  <si>
+    <t>0.0076,0.0156,0.9831,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.0078,0.9941,0.0002</t>
+  </si>
+  <si>
+    <t>0.0052,0.9856,0.0664,0.0001</t>
+  </si>
+  <si>
+    <t>0.0886,0.8356,0.1372,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.0570,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9893,0.2828,0.0000</t>
+  </si>
+  <si>
+    <t>0.1419,0.7652,0.1148,0.0016</t>
+  </si>
+  <si>
+    <t>0.0504,0.9019,0.0968,0.0006</t>
+  </si>
+  <si>
+    <t>0.0157,0.9574,0.1085,0.0003</t>
+  </si>
+  <si>
+    <t>0.0065,0.9792,0.1018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0163,0.9533,0.1870,0.0009</t>
+  </si>
+  <si>
+    <t>0.1178,0.5669,0.3717,0.0030</t>
+  </si>
+  <si>
+    <t>0.0081,0.8602,0.6703,0.0004</t>
+  </si>
+  <si>
+    <t>0.0283,0.0848,0.9103,0.0005</t>
+  </si>
+  <si>
+    <t>0.0075,0.8688,0.6258,0.0003</t>
+  </si>
+  <si>
+    <t>0.0029,0.9951,0.0165,0.0001</t>
+  </si>
+  <si>
+    <t>0.0050,0.8218,0.7865,0.0003</t>
+  </si>
+  <si>
+    <t>0.1156,0.8685,0.0652,0.0074</t>
+  </si>
+  <si>
+    <t>0.0007,0.9987,0.0133,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9971,0.0555,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9991,0.0189,0.0000</t>
+  </si>
+  <si>
+    <t>0.0046,0.5866,0.8946,0.0004</t>
+  </si>
+  <si>
+    <t>0.0062,0.8092,0.7841,0.0004</t>
+  </si>
+  <si>
+    <t>0.0317,0.0397,0.9303,0.0005</t>
+  </si>
+  <si>
+    <t>0.0078,0.0080,0.9861,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.2749,0.9661,0.0002</t>
+  </si>
+  <si>
+    <t>0.0308,0.1729,0.8678,0.0008</t>
+  </si>
+  <si>
+    <t>0.0785,0.8684,0.0767,0.0008</t>
+  </si>
+  <si>
+    <t>0.3186,0.6074,0.0652,0.0021</t>
+  </si>
+  <si>
+    <t>0.1633,0.7953,0.0467,0.0012</t>
+  </si>
+  <si>
+    <t>0.0016,0.2545,0.9797,0.0001</t>
+  </si>
+  <si>
+    <t>0.6034,0.3832,0.0281,0.0022</t>
+  </si>
+  <si>
+    <t>0.7054,0.3169,0.0161,0.0019</t>
+  </si>
+  <si>
+    <t>0.0343,0.9357,0.0632,0.0005</t>
+  </si>
+  <si>
+    <t>0.0025,0.9896,0.1433,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.1943,0.9893,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.9416,0.4489,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.9900,0.3399,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0393,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0132,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.0153,0.5164,0.7870,0.0003</t>
+  </si>
+  <si>
+    <t>0.0327,0.8849,0.2154,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.5754,0.9568,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9743,0.5145,0.0001</t>
+  </si>
+  <si>
+    <t>0.0050,0.9873,0.1097,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.9904,0.0993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.9916,0.1238,0.0001</t>
+  </si>
+  <si>
+    <t>0.2638,0.0027,0.3702,0.3522</t>
+  </si>
+  <si>
+    <t>0.0113,0.0019,0.0101,0.9914</t>
+  </si>
+  <si>
+    <t>0.0128,0.0024,0.0110,0.9899</t>
+  </si>
+  <si>
+    <t>0.2864,0.0036,0.1605,0.5420</t>
+  </si>
+  <si>
+    <t>0.2922,0.0031,0.2926,0.3854</t>
+  </si>
+  <si>
+    <t>0.0240,0.0055,0.0151,0.9799</t>
+  </si>
+  <si>
+    <t>0.0015,0.9898,0.2267,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.9719,0.4313,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.9474,0.7179,0.0001</t>
+  </si>
+  <si>
+    <t>0.0064,0.9591,0.3173,0.0008</t>
+  </si>
+  <si>
+    <t>0.0021,0.9755,0.4511,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9832,0.4877,0.0000</t>
+  </si>
+  <si>
+    <t>0.3752,0.5668,0.0476,0.0018</t>
+  </si>
+  <si>
+    <t>0.2233,0.7188,0.0518,0.0012</t>
+  </si>
+  <si>
+    <t>0.0826,0.8640,0.0729,0.0008</t>
+  </si>
+  <si>
+    <t>0.6830,0.3242,0.0193,0.0023</t>
+  </si>
+  <si>
+    <t>0.4423,0.5491,0.0296,0.0018</t>
+  </si>
+  <si>
+    <t>0.9073,0.0936,0.0065,0.0016</t>
+  </si>
+  <si>
+    <t>0.4699,0.5267,0.0272,0.0016</t>
+  </si>
+  <si>
+    <t>0.1750,0.7627,0.0639,0.0015</t>
+  </si>
+  <si>
+    <t>0.9661,0.0322,0.0022,0.0014</t>
+  </si>
+  <si>
+    <t>0.7268,0.3054,0.0126,0.0015</t>
+  </si>
+  <si>
+    <t>0.9231,0.0803,0.0043,0.0018</t>
+  </si>
+  <si>
+    <t>0.7987,0.2080,0.0138,0.0019</t>
+  </si>
+  <si>
+    <t>0.7860,0.2201,0.0146,0.0023</t>
+  </si>
+  <si>
+    <t>0.8274,0.1584,0.0151,0.0019</t>
+  </si>
+  <si>
+    <t>0.8307,0.1830,0.0096,0.0019</t>
+  </si>
+  <si>
+    <t>0.9316,0.0697,0.0045,0.0017</t>
+  </si>
+  <si>
+    <t>0.0001,0.0215,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.2134,0.9784,0.0001</t>
+  </si>
+  <si>
+    <t>0.1505,0.5569,0.3096,0.0032</t>
+  </si>
+  <si>
+    <t>0.0322,0.4187,0.7190,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0198,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9980,0.0229,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9972,0.0349,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9947,0.0394,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0282,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0074,0.0000</t>
+  </si>
+  <si>
+    <t>0.0072,0.9827,0.0541,0.0001</t>
+  </si>
+  <si>
+    <t>0.0382,0.8796,0.2164,0.0007</t>
+  </si>
+  <si>
+    <t>0.2800,0.0352,0.6374,0.0021</t>
+  </si>
+  <si>
+    <t>0.0526,0.6319,0.4668,0.0013</t>
+  </si>
+  <si>
+    <t>0.1835,0.3060,0.4341,0.0021</t>
+  </si>
+  <si>
+    <t>0.1205,0.7113,0.2966,0.0081</t>
+  </si>
+  <si>
+    <t>0.0004,0.9992,0.0135,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9989,0.0073,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9983,0.0104,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0117,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9963,0.0369,0.0000</t>
+  </si>
+  <si>
+    <t>0.0244,0.9366,0.1202,0.0004</t>
+  </si>
+  <si>
+    <t>0.0135,0.9606,0.1182,0.0002</t>
+  </si>
+  <si>
+    <t>0.3649,0.6396,0.0243,0.0012</t>
+  </si>
+  <si>
+    <t>0.6301,0.4122,0.0155,0.0019</t>
+  </si>
+  <si>
+    <t>0.7510,0.2716,0.0143,0.0020</t>
+  </si>
+  <si>
+    <t>0.6977,0.3305,0.0154,0.0018</t>
+  </si>
+  <si>
+    <t>0.5318,0.4968,0.0187,0.0014</t>
+  </si>
+  <si>
+    <t>0.2806,0.6993,0.0342,0.0012</t>
+  </si>
+  <si>
+    <t>0.8911,0.1035,0.0093,0.0022</t>
+  </si>
+  <si>
+    <t>0.7101,0.2848,0.0243,0.0022</t>
+  </si>
+  <si>
+    <t>0.0003,0.9640,0.8072,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.8937,0.7928,0.0001</t>
+  </si>
+  <si>
+    <t>0.0051,0.8540,0.7347,0.0003</t>
+  </si>
+  <si>
+    <t>0.0312,0.7274,0.5712,0.0012</t>
+  </si>
+  <si>
+    <t>0.1243,0.5848,0.3115,0.0019</t>
+  </si>
+  <si>
+    <t>0.0779,0.8499,0.1477,0.0017</t>
+  </si>
+  <si>
+    <t>0.0794,0.0145,0.9097,0.0007</t>
+  </si>
+  <si>
+    <t>0.0522,0.8157,0.2530,0.0008</t>
+  </si>
+  <si>
+    <t>0.3789,0.0091,0.0455,0.5218</t>
+  </si>
+  <si>
+    <t>0.0003,0.0014,0.0012,0.9998</t>
+  </si>
+  <si>
+    <t>0.0094,0.0162,0.0136,0.9908</t>
+  </si>
+  <si>
+    <t>0.0574,0.0036,0.0678,0.9309</t>
+  </si>
+  <si>
+    <t>0.0013,0.9944,0.1223,0.0000</t>
+  </si>
+  <si>
+    <t>0.5420,0.4980,0.0175,0.0017</t>
+  </si>
+  <si>
+    <t>0.0082,0.9882,0.0157,0.0001</t>
+  </si>
+  <si>
+    <t>0.4109,0.5842,0.0312,0.0020</t>
+  </si>
+  <si>
+    <t>0.0120,0.9779,0.0331,0.0001</t>
+  </si>
+  <si>
+    <t>0.5928,0.3927,0.0345,0.0033</t>
+  </si>
+  <si>
+    <t>0.7958,0.0584,0.0761,0.0155</t>
+  </si>
+  <si>
+    <t>0.5277,0.4926,0.0226,0.0017</t>
+  </si>
+  <si>
+    <t>0.0015,0.5177,0.9488,0.0002</t>
+  </si>
+  <si>
+    <t>0.9671,0.0098,0.0049,0.0053</t>
+  </si>
+  <si>
+    <t>0.4298,0.5385,0.0415,0.0025</t>
+  </si>
+  <si>
+    <t>0.0024,0.9867,0.1469,0.0001</t>
+  </si>
+  <si>
+    <t>0.0656,0.9015,0.0639,0.0007</t>
+  </si>
+  <si>
+    <t>0.0757,0.8338,0.1613,0.0012</t>
+  </si>
+  <si>
+    <t>0.0161,0.9756,0.0392,0.0003</t>
+  </si>
+  <si>
+    <t>0.0703,0.7542,0.2784,0.0010</t>
+  </si>
+  <si>
+    <t>0.0262,0.9168,0.1678,0.0004</t>
+  </si>
+  <si>
+    <t>0.8204,0.1867,0.0116,0.0020</t>
+  </si>
+  <si>
+    <t>0.9340,0.0558,0.0064,0.0021</t>
+  </si>
+  <si>
+    <t>0.9332,0.0646,0.0047,0.0014</t>
+  </si>
+  <si>
+    <t>0.8911,0.1069,0.0083,0.0017</t>
+  </si>
+  <si>
+    <t>0.5782,0.3508,0.0518,0.0028</t>
+  </si>
+  <si>
+    <t>0.4233,0.5811,0.0284,0.0018</t>
+  </si>
+  <si>
+    <t>0.8720,0.1380,0.0079,0.0020</t>
+  </si>
+  <si>
+    <t>0.9008,0.1002,0.0075,0.0018</t>
+  </si>
+  <si>
+    <t>0.0024,0.9925,0.0629,0.0000</t>
+  </si>
+  <si>
+    <t>0.0146,0.9702,0.0446,0.0002</t>
+  </si>
+  <si>
+    <t>0.0095,0.9813,0.0343,0.0001</t>
+  </si>
+  <si>
+    <t>0.0283,0.7088,0.5419,0.0005</t>
+  </si>
+  <si>
+    <t>0.1134,0.8503,0.0467,0.0009</t>
+  </si>
+  <si>
+    <t>0.1376,0.8135,0.0642,0.0017</t>
+  </si>
+  <si>
+    <t>0.0696,0.8917,0.0587,0.0008</t>
+  </si>
+  <si>
+    <t>0.0456,0.9283,0.0497,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.1718,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.1369,0.7781,0.1091,0.0021</t>
+  </si>
+  <si>
+    <t>0.0002,0.0193,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0064,0.7770,0.7789,0.0004</t>
+  </si>
+  <si>
+    <t>0.0106,0.0647,0.9607,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.7755,0.9134,0.0001</t>
+  </si>
+  <si>
+    <t>0.0428,0.0631,0.8812,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0189,0.9965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0097,0.1203,0.9487,0.0002</t>
+  </si>
+  <si>
+    <t>0.0191,0.7325,0.5908,0.0004</t>
+  </si>
+  <si>
+    <t>0.0169,0.4908,0.7700,0.0003</t>
+  </si>
+  <si>
+    <t>0.0304,0.3910,0.7319,0.0004</t>
+  </si>
+  <si>
+    <t>0.0433,0.8084,0.3087,0.0008</t>
+  </si>
+  <si>
+    <t>0.0113,0.9650,0.1303,0.0002</t>
+  </si>
+  <si>
+    <t>0.0558,0.8509,0.1885,0.0011</t>
+  </si>
+  <si>
+    <t>0.0693,0.7812,0.2711,0.0017</t>
+  </si>
+  <si>
+    <t>0.0721,0.7433,0.2865,0.0013</t>
+  </si>
+  <si>
+    <t>0.0042,0.9872,0.0759,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9972,0.0429,0.0000</t>
+  </si>
+  <si>
+    <t>0.0069,0.9823,0.0664,0.0001</t>
+  </si>
+  <si>
+    <t>0.0486,0.9155,0.0585,0.0005</t>
+  </si>
+  <si>
+    <t>0.0332,0.9466,0.0390,0.0004</t>
+  </si>
+  <si>
+    <t>0.0375,0.9158,0.1361,0.0007</t>
+  </si>
+  <si>
+    <t>0.3563,0.1050,0.4434,0.0034</t>
+  </si>
+  <si>
+    <t>0.1978,0.2486,0.4689,0.0021</t>
+  </si>
+  <si>
+    <t>0.0583,0.2621,0.7086,0.0008</t>
+  </si>
+  <si>
+    <t>0.1985,0.2276,0.4946,0.0028</t>
+  </si>
+  <si>
+    <t>0.0003,0.2490,0.9903,0.0000</t>
+  </si>
+  <si>
+    <t>0.0901,0.3103,0.6399,0.0025</t>
+  </si>
+  <si>
+    <t>0.0086,0.7374,0.7598,0.0004</t>
+  </si>
+  <si>
+    <t>0.0120,0.8174,0.6507,0.0007</t>
+  </si>
+  <si>
+    <t>0.0427,0.7593,0.4493,0.0031</t>
+  </si>
+  <si>
+    <t>0.8102,0.2128,0.0094,0.0016</t>
+  </si>
+  <si>
+    <t>0.4412,0.5603,0.0278,0.0016</t>
+  </si>
+  <si>
+    <t>0.5183,0.4566,0.0319,0.0019</t>
+  </si>
+  <si>
+    <t>0.2296,0.7137,0.0502,0.0013</t>
+  </si>
+  <si>
+    <t>0.3202,0.6269,0.0462,0.0016</t>
+  </si>
+  <si>
+    <t>0.3742,0.6136,0.0297,0.0014</t>
+  </si>
+  <si>
+    <t>0.8390,0.1790,0.0087,0.0018</t>
+  </si>
+  <si>
+    <t>0.5855,0.4090,0.0265,0.0021</t>
+  </si>
+  <si>
+    <t>0.0057,0.1415,0.9627,0.0002</t>
+  </si>
+  <si>
+    <t>0.0730,0.8201,0.1892,0.0012</t>
+  </si>
+  <si>
+    <t>0.2163,0.4735,0.2917,0.0030</t>
+  </si>
+  <si>
+    <t>0.0012,0.0366,0.9931,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.5748,0.9367,0.0001</t>
+  </si>
+  <si>
+    <t>0.0200,0.5520,0.7316,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.1466,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0103,0.4373,0.8478,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0734,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0225,0.1651,0.8829,0.0006</t>
+  </si>
+  <si>
+    <t>0.0016,0.7195,0.9123,0.0001</t>
+  </si>
+  <si>
+    <t>0.0691,0.4842,0.5287,0.0011</t>
+  </si>
+  <si>
+    <t>0.2317,0.0579,0.6257,0.0017</t>
+  </si>
+  <si>
+    <t>0.2064,0.5187,0.2406,0.0021</t>
+  </si>
+  <si>
+    <t>0.1863,0.7812,0.0417,0.0013</t>
+  </si>
+  <si>
+    <t>0.4623,0.4835,0.0431,0.0021</t>
+  </si>
+  <si>
+    <t>0.6987,0.3014,0.0196,0.0019</t>
+  </si>
+  <si>
+    <t>0.3601,0.5422,0.0668,0.0020</t>
+  </si>
+  <si>
+    <t>0.6297,0.4178,0.0130,0.0015</t>
+  </si>
+  <si>
+    <t>0.1465,0.7918,0.0654,0.0012</t>
+  </si>
+  <si>
+    <t>0.3849,0.6234,0.0235,0.0013</t>
+  </si>
+  <si>
+    <t>0.7563,0.2610,0.0135,0.0020</t>
+  </si>
+  <si>
+    <t>0.0310,0.6576,0.5551,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.4179,0.9743,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.6626,0.9505,0.0001</t>
+  </si>
+  <si>
+    <t>0.0362,0.8518,0.3071,0.0010</t>
+  </si>
+  <si>
+    <t>0.0076,0.1760,0.9469,0.0005</t>
+  </si>
+  <si>
+    <t>0.1321,0.1920,0.6081,0.0017</t>
+  </si>
+  <si>
+    <t>0.0125,0.1430,0.9344,0.0003</t>
+  </si>
+  <si>
+    <t>0.1901,0.3059,0.4476,0.0046</t>
+  </si>
+  <si>
+    <t>0.7879,0.1479,0.0429,0.0071</t>
+  </si>
+  <si>
+    <t>0.1702,0.0084,0.1989,0.7249</t>
+  </si>
+  <si>
+    <t>0.6002,0.0121,0.0795,0.1980</t>
+  </si>
+  <si>
+    <t>0.0356,0.0017,0.0445,0.9602</t>
+  </si>
+  <si>
+    <t>0.0228,0.0025,0.0286,0.9777</t>
+  </si>
+  <si>
+    <t>0.2264,0.6561,0.1588,0.0065</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1973,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,10 +2040,10 @@
         <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,10 +2068,10 @@
         <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2141,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2180,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2337,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>262</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2477,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2505,7 @@
         <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2533,7 @@
         <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2575,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>262</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>262</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>262</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,10 +2782,10 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2908,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>263</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2967,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3023,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3051,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3079,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>262</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3121,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3135,7 @@
         <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>262</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>262</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>262</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,10 +3230,10 @@
         <v>259</v>
       </c>
       <c r="C93" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,10 +3258,10 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>262</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,10 +3370,10 @@
         <v>259</v>
       </c>
       <c r="C103" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3426,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3569,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3611,7 @@
         <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>262</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,10 +3748,10 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>262</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,10 +3818,10 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3835,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3849,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3888,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>262</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3919,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>262</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3975,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3989,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,10 +4042,10 @@
         <v>259</v>
       </c>
       <c r="C151" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>263</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,10 +4140,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>262</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,10 +4308,10 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>262</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>262</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>262</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>262</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4647,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4717,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4784,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4798,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4812,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4826,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4857,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4871,7 @@
         <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4885,7 @@
         <v>263</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,10 +4924,10 @@
         <v>259</v>
       </c>
       <c r="C214" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>262</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,10 +4966,10 @@
         <v>259</v>
       </c>
       <c r="C217" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,10 +4980,10 @@
         <v>259</v>
       </c>
       <c r="C218" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5039,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,10 +5050,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>263</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5095,7 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5165,7 @@
         <v>263</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5176,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5204,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,10 +5218,10 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,10 +5232,10 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>262</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>262</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>262</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5403,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5417,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5459,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5473,7 @@
         <v>259</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5487,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5501,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5512,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
